--- a/Thesis Forecasting/metadata/random_forest/testing_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/random_forest/testing_average_metrics.xlsx
@@ -421,8 +421,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.486362417005194</v>
+        <v>3.377216762221778</v>
       </c>
       <c r="E2" t="n">
-        <v>1.875336494578505</v>
+        <v>1.83697522051419</v>
       </c>
       <c r="F2" t="n">
-        <v>3.427619689013735</v>
+        <v>3.3902379831123</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8996038657827569</v>
+        <v>0.9017817700204243</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D3" t="n">
-        <v>2.161182022518592</v>
+        <v>2.360647957762337</v>
       </c>
       <c r="E3" t="n">
-        <v>1.933811975752544</v>
+        <v>2.057751859712116</v>
       </c>
       <c r="F3" t="n">
-        <v>5.005367101266894</v>
+        <v>4.894579628714905</v>
       </c>
       <c r="G3" t="n">
-        <v>0.904776404097143</v>
+        <v>0.9089450616528172</v>
       </c>
     </row>
     <row r="4">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D4" t="n">
-        <v>1.164311265066937</v>
+        <v>0.8368764813740764</v>
       </c>
       <c r="E4" t="n">
-        <v>1.365183498334776</v>
+        <v>0.9950894832429902</v>
       </c>
       <c r="F4" t="n">
-        <v>3.454070031467231</v>
+        <v>2.926018781429621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9311114849194968</v>
+        <v>0.9505645189020273</v>
       </c>
     </row>
     <row r="5">
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D5" t="n">
-        <v>4.200484513643534</v>
+        <v>4.08064247874045</v>
       </c>
       <c r="E5" t="n">
-        <v>1.598433789599624</v>
+        <v>1.572321523955471</v>
       </c>
       <c r="F5" t="n">
-        <v>2.268945184641984</v>
+        <v>2.192159151310138</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8932760677734746</v>
+        <v>0.9003773769971353</v>
       </c>
     </row>
     <row r="6">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>19.87941386644245</v>
+        <v>4.14007245328403</v>
       </c>
       <c r="E6" t="n">
-        <v>8.033408364487512</v>
+        <v>2.912237979858503</v>
       </c>
       <c r="F6" t="n">
-        <v>12.19846815910361</v>
+        <v>6.080681074686011</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9560946692216128</v>
+        <v>0.9890903426365119</v>
       </c>
     </row>
     <row r="7">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D7" t="n">
-        <v>4.294212888621112</v>
+        <v>4.149024259946129</v>
       </c>
       <c r="E7" t="n">
-        <v>1.526733463455669</v>
+        <v>1.47161523248911</v>
       </c>
       <c r="F7" t="n">
-        <v>2.174929166543046</v>
+        <v>2.076160785216743</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9112685527839555</v>
+        <v>0.9191445501317088</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/metadata/random_forest/testing_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/random_forest/testing_average_metrics.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,37 +440,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
